--- a/formulas_activas.xlsx
+++ b/formulas_activas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agpglass-my.sharepoint.com/personal/abotero_agpglass_com/Documents/Documentos/MODULO_5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9407" documentId="13_ncr:1_{9FD8E549-24C7-4023-93CE-6DC6B55769EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E49CF6-FF6E-4F5E-82AF-2B997647DE7B}"/>
+  <xr:revisionPtr revIDLastSave="9411" documentId="13_ncr:1_{9FD8E549-24C7-4023-93CE-6DC6B55769EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF3E82EE-9133-40B5-AB5D-8D9D11D67162}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="691" activeTab="1" xr2:uid="{98CEF0ED-E329-4DDB-BB56-BCA74AB6D55B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="691" xr2:uid="{98CEF0ED-E329-4DDB-BB56-BCA74AB6D55B}"/>
   </bookViews>
   <sheets>
     <sheet name="CAM" sheetId="5" r:id="rId1"/>
@@ -2358,15 +2358,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2377,6 +2368,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,6 +2451,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2770,7 +2774,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8C699D-BC39-450F-9879-6A3CE12FA813}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:EU298"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2794,39 +2797,39 @@
   <sheetData>
     <row r="1" spans="2:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="88"/>
-      <c r="C1" s="121" t="s">
+      <c r="C1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
       <c r="F1" s="61"/>
-      <c r="G1" s="121" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="121" t="s">
+      <c r="G1" s="118" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
     </row>
     <row r="2" spans="2:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="87"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
       <c r="F2" s="60"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="34"/>
@@ -2840,19 +2843,19 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L4" s="122" t="s">
+      <c r="L4" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="122"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="119"/>
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
       <c r="W4" s="35"/>
     </row>
     <row r="5" spans="2:23" ht="150" customHeight="1" x14ac:dyDescent="0.3">
@@ -2920,7 +2923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
@@ -2973,7 +2976,7 @@
       <c r="U6" s="31"/>
       <c r="V6" s="31"/>
     </row>
-    <row r="7" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>34</v>
       </c>
@@ -3026,7 +3029,7 @@
       <c r="U7" s="84"/>
       <c r="V7" s="84"/>
     </row>
-    <row r="8" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="82" t="s">
         <v>34</v>
       </c>
@@ -3075,7 +3078,7 @@
       <c r="U8" s="84"/>
       <c r="V8" s="84"/>
     </row>
-    <row r="9" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="82" t="s">
         <v>34</v>
       </c>
@@ -3128,7 +3131,7 @@
       <c r="U9" s="84"/>
       <c r="V9" s="84"/>
     </row>
-    <row r="10" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
@@ -3181,7 +3184,7 @@
       <c r="U10" s="31"/>
       <c r="V10" s="31"/>
     </row>
-    <row r="11" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>42</v>
       </c>
@@ -3230,7 +3233,7 @@
       <c r="U11" s="31"/>
       <c r="V11" s="31"/>
     </row>
-    <row r="12" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>42</v>
       </c>
@@ -3283,7 +3286,7 @@
       <c r="U12" s="31"/>
       <c r="V12" s="31"/>
     </row>
-    <row r="13" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="82" t="s">
         <v>44</v>
       </c>
@@ -3336,7 +3339,7 @@
       <c r="U13" s="84"/>
       <c r="V13" s="84"/>
     </row>
-    <row r="14" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="82" t="s">
         <v>44</v>
       </c>
@@ -3385,7 +3388,7 @@
       <c r="U14" s="84"/>
       <c r="V14" s="84"/>
     </row>
-    <row r="15" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="82" t="s">
         <v>44</v>
       </c>
@@ -3440,7 +3443,7 @@
       <c r="U15" s="84"/>
       <c r="V15" s="84"/>
     </row>
-    <row r="16" spans="2:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="74" t="s">
         <v>46</v>
       </c>
@@ -3493,7 +3496,7 @@
       <c r="U16" s="31"/>
       <c r="V16" s="31"/>
     </row>
-    <row r="17" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="74" t="s">
         <v>46</v>
       </c>
@@ -3542,7 +3545,7 @@
       <c r="U17" s="31"/>
       <c r="V17" s="31"/>
     </row>
-    <row r="18" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="74" t="s">
         <v>46</v>
       </c>
@@ -3595,7 +3598,7 @@
       <c r="U18" s="31"/>
       <c r="V18" s="31"/>
     </row>
-    <row r="19" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="82" t="s">
         <v>48</v>
       </c>
@@ -3648,7 +3651,7 @@
       <c r="U19" s="84"/>
       <c r="V19" s="84"/>
     </row>
-    <row r="20" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="82" t="s">
         <v>48</v>
       </c>
@@ -3697,7 +3700,7 @@
       <c r="U20" s="84"/>
       <c r="V20" s="84"/>
     </row>
-    <row r="21" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="82" t="s">
         <v>48</v>
       </c>
@@ -3750,7 +3753,7 @@
       <c r="U21" s="84"/>
       <c r="V21" s="84"/>
     </row>
-    <row r="22" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="12" t="s">
         <v>50</v>
       </c>
@@ -3805,7 +3808,7 @@
       <c r="U22" s="31"/>
       <c r="V22" s="31"/>
     </row>
-    <row r="23" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="77" t="s">
         <v>52</v>
       </c>
@@ -3856,7 +3859,7 @@
       <c r="U23" s="78"/>
       <c r="V23" s="78"/>
     </row>
-    <row r="24" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="77" t="s">
         <v>52</v>
       </c>
@@ -3905,7 +3908,7 @@
       <c r="U24" s="78"/>
       <c r="V24" s="78"/>
     </row>
-    <row r="25" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="77" t="s">
         <v>52</v>
       </c>
@@ -3952,7 +3955,7 @@
       <c r="U25" s="84"/>
       <c r="V25" s="84"/>
     </row>
-    <row r="26" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="77" t="s">
         <v>52</v>
       </c>
@@ -4007,7 +4010,7 @@
       <c r="U26" s="84"/>
       <c r="V26" s="84"/>
     </row>
-    <row r="27" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="77" t="s">
         <v>52</v>
       </c>
@@ -4054,7 +4057,7 @@
       <c r="U27" s="84"/>
       <c r="V27" s="84"/>
     </row>
-    <row r="28" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
         <v>59</v>
       </c>
@@ -4107,7 +4110,7 @@
       <c r="U28" s="31"/>
       <c r="V28" s="31"/>
     </row>
-    <row r="29" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="77" t="s">
         <v>61</v>
       </c>
@@ -4160,7 +4163,7 @@
       <c r="U29" s="84"/>
       <c r="V29" s="84"/>
     </row>
-    <row r="30" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
         <v>63</v>
       </c>
@@ -4213,7 +4216,7 @@
       <c r="U30" s="31"/>
       <c r="V30" s="31"/>
     </row>
-    <row r="31" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="77" t="s">
         <v>65</v>
       </c>
@@ -4266,7 +4269,7 @@
       <c r="U31" s="84"/>
       <c r="V31" s="84"/>
     </row>
-    <row r="32" spans="2:22" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
         <v>25</v>
       </c>
@@ -4317,7 +4320,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>25</v>
       </c>
@@ -4360,7 +4363,7 @@
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
     </row>
-    <row r="34" spans="2:27" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:27" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="82" t="s">
         <v>34</v>
       </c>
@@ -4411,7 +4414,7 @@
       <c r="U34" s="78"/>
       <c r="V34" s="78"/>
     </row>
-    <row r="35" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="82" t="s">
         <v>34</v>
       </c>
@@ -4466,7 +4469,7 @@
       <c r="U35" s="78"/>
       <c r="V35" s="78"/>
     </row>
-    <row r="36" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>42</v>
       </c>
@@ -4517,7 +4520,7 @@
       <c r="U36" s="19"/>
       <c r="V36" s="19"/>
     </row>
-    <row r="37" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>42</v>
       </c>
@@ -4572,7 +4575,7 @@
       <c r="X37" s="18"/>
       <c r="Y37" s="18"/>
     </row>
-    <row r="38" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="82" t="s">
         <v>44</v>
       </c>
@@ -4625,7 +4628,7 @@
       <c r="X38" s="18"/>
       <c r="Y38" s="18"/>
     </row>
-    <row r="39" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="82" t="s">
         <v>44</v>
       </c>
@@ -4680,7 +4683,7 @@
       <c r="X39" s="26"/>
       <c r="Y39" s="18"/>
     </row>
-    <row r="40" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74" t="s">
         <v>46</v>
       </c>
@@ -4733,7 +4736,7 @@
       <c r="X40" s="18"/>
       <c r="Y40" s="18"/>
     </row>
-    <row r="41" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74" t="s">
         <v>46</v>
       </c>
@@ -4790,7 +4793,7 @@
       <c r="Z41" s="18"/>
       <c r="AA41" s="18"/>
     </row>
-    <row r="42" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="82" t="s">
         <v>48</v>
       </c>
@@ -4845,7 +4848,7 @@
       <c r="Z42" s="18"/>
       <c r="AA42" s="18"/>
     </row>
-    <row r="43" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="82" t="s">
         <v>48</v>
       </c>
@@ -4902,7 +4905,7 @@
       <c r="Z43" s="18"/>
       <c r="AA43" s="18"/>
     </row>
-    <row r="44" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="12" t="s">
         <v>50</v>
       </c>
@@ -4957,7 +4960,7 @@
       <c r="Z44" s="18"/>
       <c r="AA44" s="18"/>
     </row>
-    <row r="45" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="77" t="s">
         <v>52</v>
       </c>
@@ -5014,7 +5017,7 @@
       <c r="Z45" s="18"/>
       <c r="AA45" s="18"/>
     </row>
-    <row r="46" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="77" t="s">
         <v>52</v>
       </c>
@@ -5067,7 +5070,7 @@
       <c r="Z46" s="18"/>
       <c r="AA46" s="18"/>
     </row>
-    <row r="47" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="77" t="s">
         <v>52</v>
       </c>
@@ -5120,7 +5123,7 @@
       <c r="Z47" s="18"/>
       <c r="AA47" s="18"/>
     </row>
-    <row r="48" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="12" t="s">
         <v>59</v>
       </c>
@@ -5175,7 +5178,7 @@
       <c r="Z48" s="18"/>
       <c r="AA48" s="18"/>
     </row>
-    <row r="49" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="77" t="s">
         <v>61</v>
       </c>
@@ -5232,7 +5235,7 @@
       <c r="Z49" s="18"/>
       <c r="AA49" s="18"/>
     </row>
-    <row r="50" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="12" t="s">
         <v>63</v>
       </c>
@@ -5287,7 +5290,7 @@
       <c r="Z50" s="26"/>
       <c r="AA50" s="26"/>
     </row>
-    <row r="51" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="77" t="s">
         <v>65</v>
       </c>
@@ -5342,7 +5345,7 @@
       <c r="Z51" s="26"/>
       <c r="AA51" s="26"/>
     </row>
-    <row r="52" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="12" t="s">
         <v>25</v>
       </c>
@@ -5400,7 +5403,7 @@
       <c r="Z52" s="18"/>
       <c r="AA52" s="18"/>
     </row>
-    <row r="53" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="12" t="s">
         <v>25</v>
       </c>
@@ -5452,7 +5455,7 @@
       <c r="Z53" s="18"/>
       <c r="AA53" s="18"/>
     </row>
-    <row r="54" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="82" t="s">
         <v>34</v>
       </c>
@@ -5624,7 +5627,7 @@
       <c r="Z56" s="18"/>
       <c r="AA56" s="18"/>
     </row>
-    <row r="57" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>42</v>
       </c>
@@ -5796,7 +5799,7 @@
       <c r="Z59" s="18"/>
       <c r="AA59" s="18"/>
     </row>
-    <row r="60" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="82" t="s">
         <v>44</v>
       </c>
@@ -5858,7 +5861,7 @@
       <c r="Z60" s="18"/>
       <c r="AA60" s="18"/>
     </row>
-    <row r="61" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="82" t="s">
         <v>44</v>
       </c>
@@ -5912,7 +5915,7 @@
       <c r="Z61" s="18"/>
       <c r="AA61" s="18"/>
     </row>
-    <row r="62" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="82" t="s">
         <v>44</v>
       </c>
@@ -5968,7 +5971,7 @@
       <c r="Z62" s="18"/>
       <c r="AA62" s="18"/>
     </row>
-    <row r="63" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74" t="s">
         <v>46</v>
       </c>
@@ -6030,7 +6033,7 @@
       <c r="Z63" s="18"/>
       <c r="AA63" s="18"/>
     </row>
-    <row r="64" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74" t="s">
         <v>46</v>
       </c>
@@ -6084,7 +6087,7 @@
       <c r="Z64" s="18"/>
       <c r="AA64" s="18"/>
     </row>
-    <row r="65" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74" t="s">
         <v>46</v>
       </c>
@@ -6140,7 +6143,7 @@
       <c r="Z65" s="18"/>
       <c r="AA65" s="18"/>
     </row>
-    <row r="66" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="82" t="s">
         <v>48</v>
       </c>
@@ -6202,7 +6205,7 @@
       <c r="Z66" s="18"/>
       <c r="AA66" s="18"/>
     </row>
-    <row r="67" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="82" t="s">
         <v>48</v>
       </c>
@@ -6256,7 +6259,7 @@
       <c r="Z67" s="18"/>
       <c r="AA67" s="18"/>
     </row>
-    <row r="68" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="82" t="s">
         <v>48</v>
       </c>
@@ -6312,7 +6315,7 @@
       <c r="Z68" s="18"/>
       <c r="AA68" s="18"/>
     </row>
-    <row r="69" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="12" t="s">
         <v>50</v>
       </c>
@@ -6370,7 +6373,7 @@
       <c r="Z69" s="18"/>
       <c r="AA69" s="18"/>
     </row>
-    <row r="70" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="77" t="s">
         <v>52</v>
       </c>
@@ -6422,7 +6425,7 @@
       <c r="Z70" s="18"/>
       <c r="AA70" s="18"/>
     </row>
-    <row r="71" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="77" t="s">
         <v>52</v>
       </c>
@@ -6478,7 +6481,7 @@
       <c r="Z71" s="18"/>
       <c r="AA71" s="18"/>
     </row>
-    <row r="72" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="77" t="s">
         <v>52</v>
       </c>
@@ -6538,7 +6541,7 @@
       <c r="Z72" s="18"/>
       <c r="AA72" s="18"/>
     </row>
-    <row r="73" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="77" t="s">
         <v>52</v>
       </c>
@@ -6600,7 +6603,7 @@
       <c r="Z73" s="18"/>
       <c r="AA73" s="18"/>
     </row>
-    <row r="74" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="77" t="s">
         <v>52</v>
       </c>
@@ -6652,7 +6655,7 @@
       <c r="Z74" s="18"/>
       <c r="AA74" s="18"/>
     </row>
-    <row r="75" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="77" t="s">
         <v>52</v>
       </c>
@@ -6702,7 +6705,7 @@
       <c r="Z75" s="18"/>
       <c r="AA75" s="18"/>
     </row>
-    <row r="76" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="12" t="s">
         <v>59</v>
       </c>
@@ -6762,7 +6765,7 @@
       <c r="Z76" s="18"/>
       <c r="AA76" s="18"/>
     </row>
-    <row r="77" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="77" t="s">
         <v>61</v>
       </c>
@@ -6822,7 +6825,7 @@
       <c r="Z77" s="18"/>
       <c r="AA77" s="18"/>
     </row>
-    <row r="78" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="12" t="s">
         <v>63</v>
       </c>
@@ -6882,7 +6885,7 @@
       <c r="Z78" s="18"/>
       <c r="AA78" s="18"/>
     </row>
-    <row r="79" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="77" t="s">
         <v>65</v>
       </c>
@@ -6942,7 +6945,7 @@
       <c r="Z79" s="18"/>
       <c r="AA79" s="18"/>
     </row>
-    <row r="80" spans="2:27" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="12" t="s">
         <v>59</v>
       </c>
@@ -6991,7 +6994,7 @@
       <c r="W80" s="26"/>
       <c r="X80" s="26"/>
     </row>
-    <row r="81" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="77" t="s">
         <v>61</v>
       </c>
@@ -7040,7 +7043,7 @@
       <c r="W81" s="26"/>
       <c r="X81" s="26"/>
     </row>
-    <row r="82" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="12" t="s">
         <v>63</v>
       </c>
@@ -7089,7 +7092,7 @@
       <c r="W82" s="26"/>
       <c r="X82" s="26"/>
     </row>
-    <row r="83" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="77" t="s">
         <v>65</v>
       </c>
@@ -7138,7 +7141,7 @@
       <c r="W83" s="26"/>
       <c r="X83" s="26"/>
     </row>
-    <row r="84" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="12" t="s">
         <v>25</v>
       </c>
@@ -7191,7 +7194,7 @@
       <c r="AA84" s="26"/>
       <c r="AB84" s="18"/>
     </row>
-    <row r="85" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="12" t="s">
         <v>25</v>
       </c>
@@ -7244,7 +7247,7 @@
       <c r="AA85" s="26"/>
       <c r="AB85" s="18"/>
     </row>
-    <row r="86" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="82" t="s">
         <v>34</v>
       </c>
@@ -7307,7 +7310,7 @@
       <c r="AA86" s="18"/>
       <c r="AB86" s="18"/>
     </row>
-    <row r="87" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="82" t="s">
         <v>34</v>
       </c>
@@ -7362,7 +7365,7 @@
       <c r="AA87" s="26"/>
       <c r="AB87" s="18"/>
     </row>
-    <row r="88" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="82" t="s">
         <v>34</v>
       </c>
@@ -7425,7 +7428,7 @@
       <c r="AA88" s="18"/>
       <c r="AB88" s="18"/>
     </row>
-    <row r="89" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="4" t="s">
         <v>42</v>
       </c>
@@ -7488,7 +7491,7 @@
       <c r="AA89" s="18"/>
       <c r="AB89" s="18"/>
     </row>
-    <row r="90" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="4" t="s">
         <v>42</v>
       </c>
@@ -7543,7 +7546,7 @@
       <c r="AA90" s="26"/>
       <c r="AB90" s="18"/>
     </row>
-    <row r="91" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>42</v>
       </c>
@@ -7606,7 +7609,7 @@
       <c r="AA91" s="18"/>
       <c r="AB91" s="18"/>
     </row>
-    <row r="92" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="82" t="s">
         <v>44</v>
       </c>
@@ -7669,7 +7672,7 @@
       <c r="AA92" s="18"/>
       <c r="AB92" s="18"/>
     </row>
-    <row r="93" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="82" t="s">
         <v>44</v>
       </c>
@@ -7724,7 +7727,7 @@
       <c r="AA93" s="18"/>
       <c r="AB93" s="18"/>
     </row>
-    <row r="94" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="82" t="s">
         <v>44</v>
       </c>
@@ -7787,7 +7790,7 @@
       <c r="AA94" s="18"/>
       <c r="AB94" s="18"/>
     </row>
-    <row r="95" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="74" t="s">
         <v>46</v>
       </c>
@@ -7850,7 +7853,7 @@
       <c r="AA95" s="18"/>
       <c r="AB95" s="18"/>
     </row>
-    <row r="96" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="74" t="s">
         <v>46</v>
       </c>
@@ -7905,7 +7908,7 @@
       <c r="AA96" s="26"/>
       <c r="AB96" s="18"/>
     </row>
-    <row r="97" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="74" t="s">
         <v>46</v>
       </c>
@@ -7968,7 +7971,7 @@
       <c r="AA97" s="18"/>
       <c r="AB97" s="18"/>
     </row>
-    <row r="98" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="82" t="s">
         <v>48</v>
       </c>
@@ -8031,7 +8034,7 @@
       <c r="AA98" s="18"/>
       <c r="AB98" s="18"/>
     </row>
-    <row r="99" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="82" t="s">
         <v>48</v>
       </c>
@@ -8086,7 +8089,7 @@
       <c r="AA99" s="18"/>
       <c r="AB99" s="18"/>
     </row>
-    <row r="100" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="82" t="s">
         <v>48</v>
       </c>
@@ -8149,7 +8152,7 @@
       <c r="AA100" s="18"/>
       <c r="AB100" s="18"/>
     </row>
-    <row r="101" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="12" t="s">
         <v>50</v>
       </c>
@@ -8212,7 +8215,7 @@
       <c r="AA101" s="18"/>
       <c r="AB101" s="18"/>
     </row>
-    <row r="102" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="12" t="s">
         <v>50</v>
       </c>
@@ -8267,7 +8270,7 @@
       <c r="AA102" s="18"/>
       <c r="AB102" s="18"/>
     </row>
-    <row r="103" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="12" t="s">
         <v>50</v>
       </c>
@@ -8330,7 +8333,7 @@
       <c r="AA103" s="18"/>
       <c r="AB103" s="18"/>
     </row>
-    <row r="104" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="77" t="s">
         <v>52</v>
       </c>
@@ -8393,7 +8396,7 @@
       <c r="AA104" s="18"/>
       <c r="AB104" s="18"/>
     </row>
-    <row r="105" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="77" t="s">
         <v>52</v>
       </c>
@@ -8448,7 +8451,7 @@
       <c r="AA105" s="18"/>
       <c r="AB105" s="18"/>
     </row>
-    <row r="106" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="77" t="s">
         <v>52</v>
       </c>
@@ -8511,7 +8514,7 @@
       <c r="AA106" s="26"/>
       <c r="AB106" s="18"/>
     </row>
-    <row r="107" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="77" t="s">
         <v>52</v>
       </c>
@@ -8566,7 +8569,7 @@
       <c r="AA107" s="26"/>
       <c r="AB107" s="18"/>
     </row>
-    <row r="108" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="77" t="s">
         <v>52</v>
       </c>
@@ -8621,7 +8624,7 @@
       <c r="AA108" s="18"/>
       <c r="AB108" s="18"/>
     </row>
-    <row r="109" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="12" t="s">
         <v>25</v>
       </c>
@@ -8674,7 +8677,7 @@
       <c r="AC109" s="18"/>
       <c r="AD109" s="18"/>
     </row>
-    <row r="110" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="12" t="s">
         <v>25</v>
       </c>
@@ -8729,7 +8732,7 @@
       <c r="AC110" s="18"/>
       <c r="AD110" s="18"/>
     </row>
-    <row r="111" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="12" t="s">
         <v>25</v>
       </c>
@@ -8784,7 +8787,7 @@
       <c r="AC111" s="18"/>
       <c r="AD111" s="18"/>
     </row>
-    <row r="112" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="82" t="s">
         <v>34</v>
       </c>
@@ -8839,7 +8842,7 @@
       <c r="AC112" s="18"/>
       <c r="AD112" s="18"/>
     </row>
-    <row r="113" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="82" t="s">
         <v>34</v>
       </c>
@@ -8900,7 +8903,7 @@
       <c r="AC113" s="18"/>
       <c r="AD113" s="18"/>
     </row>
-    <row r="114" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="82" t="s">
         <v>34</v>
       </c>
@@ -8961,7 +8964,7 @@
       <c r="AC114" s="18"/>
       <c r="AD114" s="18"/>
     </row>
-    <row r="115" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="4" t="s">
         <v>42</v>
       </c>
@@ -9016,7 +9019,7 @@
       <c r="AC115" s="18"/>
       <c r="AD115" s="18"/>
     </row>
-    <row r="116" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="4" t="s">
         <v>42</v>
       </c>
@@ -9077,7 +9080,7 @@
       <c r="AC116" s="18"/>
       <c r="AD116" s="18"/>
     </row>
-    <row r="117" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="4" t="s">
         <v>42</v>
       </c>
@@ -9138,7 +9141,7 @@
       <c r="AC117" s="18"/>
       <c r="AD117" s="18"/>
     </row>
-    <row r="118" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="82" t="s">
         <v>44</v>
       </c>
@@ -9193,7 +9196,7 @@
       <c r="AC118" s="18"/>
       <c r="AD118" s="18"/>
     </row>
-    <row r="119" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="82" t="s">
         <v>44</v>
       </c>
@@ -9254,7 +9257,7 @@
       <c r="AC119" s="18"/>
       <c r="AD119" s="18"/>
     </row>
-    <row r="120" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="82" t="s">
         <v>44</v>
       </c>
@@ -9315,7 +9318,7 @@
       <c r="AC120" s="18"/>
       <c r="AD120" s="18"/>
     </row>
-    <row r="121" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="74" t="s">
         <v>46</v>
       </c>
@@ -9370,7 +9373,7 @@
       <c r="AC121" s="18"/>
       <c r="AD121" s="18"/>
     </row>
-    <row r="122" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="74" t="s">
         <v>46</v>
       </c>
@@ -9431,7 +9434,7 @@
       <c r="AC122" s="18"/>
       <c r="AD122" s="18"/>
     </row>
-    <row r="123" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74" t="s">
         <v>46</v>
       </c>
@@ -9492,7 +9495,7 @@
       <c r="AC123" s="18"/>
       <c r="AD123" s="18"/>
     </row>
-    <row r="124" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="82" t="s">
         <v>48</v>
       </c>
@@ -9547,7 +9550,7 @@
       <c r="AC124" s="18"/>
       <c r="AD124" s="18"/>
     </row>
-    <row r="125" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="82" t="s">
         <v>48</v>
       </c>
@@ -9608,7 +9611,7 @@
       <c r="AC125" s="18"/>
       <c r="AD125" s="18"/>
     </row>
-    <row r="126" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="82" t="s">
         <v>48</v>
       </c>
@@ -9669,7 +9672,7 @@
       <c r="AC126" s="18"/>
       <c r="AD126" s="18"/>
     </row>
-    <row r="127" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="12" t="s">
         <v>50</v>
       </c>
@@ -9730,7 +9733,7 @@
       <c r="AC127" s="18"/>
       <c r="AD127" s="18"/>
     </row>
-    <row r="128" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="77" t="s">
         <v>52</v>
       </c>
@@ -9785,7 +9788,7 @@
       <c r="AC128" s="18"/>
       <c r="AD128" s="18"/>
     </row>
-    <row r="129" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="77" t="s">
         <v>52</v>
       </c>
@@ -9846,7 +9849,7 @@
       <c r="AC129" s="18"/>
       <c r="AD129" s="18"/>
     </row>
-    <row r="130" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="77" t="s">
         <v>52</v>
       </c>
@@ -9907,7 +9910,7 @@
       <c r="AC130" s="18"/>
       <c r="AD130" s="18"/>
     </row>
-    <row r="131" spans="2:30" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="12" t="s">
         <v>25</v>
       </c>
@@ -9961,7 +9964,7 @@
       <c r="X131" s="26"/>
       <c r="Y131" s="26"/>
     </row>
-    <row r="132" spans="2:30" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:30" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="12" t="s">
         <v>25</v>
       </c>
@@ -10014,7 +10017,7 @@
       <c r="AA132" s="26"/>
       <c r="AB132" s="34"/>
     </row>
-    <row r="133" spans="2:30" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:30" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="82" t="s">
         <v>34</v>
       </c>
@@ -10073,7 +10076,7 @@
       <c r="AA133" s="26"/>
       <c r="AB133" s="34"/>
     </row>
-    <row r="134" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="82" t="s">
         <v>34</v>
       </c>
@@ -10136,7 +10139,7 @@
       <c r="AA134" s="18"/>
       <c r="AB134" s="18"/>
     </row>
-    <row r="135" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="4" t="s">
         <v>42</v>
       </c>
@@ -10199,7 +10202,7 @@
       <c r="AA135" s="18"/>
       <c r="AB135" s="18"/>
     </row>
-    <row r="136" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="4" t="s">
         <v>42</v>
       </c>
@@ -10262,7 +10265,7 @@
       <c r="AA136" s="18"/>
       <c r="AB136" s="18"/>
     </row>
-    <row r="137" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="82" t="s">
         <v>44</v>
       </c>
@@ -10325,7 +10328,7 @@
       <c r="AA137" s="18"/>
       <c r="AB137" s="18"/>
     </row>
-    <row r="138" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="82" t="s">
         <v>44</v>
       </c>
@@ -10388,7 +10391,7 @@
       <c r="AA138" s="18"/>
       <c r="AB138" s="18"/>
     </row>
-    <row r="139" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="74" t="s">
         <v>46</v>
       </c>
@@ -10451,7 +10454,7 @@
       <c r="AA139" s="18"/>
       <c r="AB139" s="18"/>
     </row>
-    <row r="140" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="74" t="s">
         <v>46</v>
       </c>
@@ -10514,7 +10517,7 @@
       <c r="AA140" s="18"/>
       <c r="AB140" s="18"/>
     </row>
-    <row r="141" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="82" t="s">
         <v>48</v>
       </c>
@@ -10577,7 +10580,7 @@
       <c r="AA141" s="18"/>
       <c r="AB141" s="18"/>
     </row>
-    <row r="142" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="82" t="s">
         <v>48</v>
       </c>
@@ -10640,7 +10643,7 @@
       <c r="AA142" s="18"/>
       <c r="AB142" s="18"/>
     </row>
-    <row r="143" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="12" t="s">
         <v>50</v>
       </c>
@@ -10703,7 +10706,7 @@
       <c r="AA143" s="18"/>
       <c r="AB143" s="18"/>
     </row>
-    <row r="144" spans="2:30" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="12" t="s">
         <v>50</v>
       </c>
@@ -10766,7 +10769,7 @@
       <c r="AA144" s="18"/>
       <c r="AB144" s="18"/>
     </row>
-    <row r="145" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="77" t="s">
         <v>52</v>
       </c>
@@ -10825,7 +10828,7 @@
       <c r="AA145" s="18"/>
       <c r="AB145" s="18"/>
     </row>
-    <row r="146" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="77" t="s">
         <v>52</v>
       </c>
@@ -10882,7 +10885,7 @@
       <c r="U146" s="84"/>
       <c r="V146" s="78"/>
     </row>
-    <row r="147" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="12" t="s">
         <v>25</v>
       </c>
@@ -10931,7 +10934,7 @@
       <c r="AA147" s="18"/>
       <c r="AB147" s="18"/>
     </row>
-    <row r="148" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="82" t="s">
         <v>34</v>
       </c>
@@ -10986,7 +10989,7 @@
       <c r="AA148" s="33"/>
       <c r="AB148" s="18"/>
     </row>
-    <row r="149" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="4" t="s">
         <v>42</v>
       </c>
@@ -11041,7 +11044,7 @@
       <c r="AA149" s="33"/>
       <c r="AB149" s="18"/>
     </row>
-    <row r="150" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="82" t="s">
         <v>44</v>
       </c>
@@ -11096,7 +11099,7 @@
       <c r="AA150" s="33"/>
       <c r="AB150" s="18"/>
     </row>
-    <row r="151" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="74" t="s">
         <v>46</v>
       </c>
@@ -11151,7 +11154,7 @@
       <c r="AA151" s="33"/>
       <c r="AB151" s="18"/>
     </row>
-    <row r="152" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="82" t="s">
         <v>48</v>
       </c>
@@ -11206,7 +11209,7 @@
       <c r="AA152" s="33"/>
       <c r="AB152" s="18"/>
     </row>
-    <row r="153" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="12" t="s">
         <v>50</v>
       </c>
@@ -11261,7 +11264,7 @@
       <c r="AA153" s="33"/>
       <c r="AB153" s="18"/>
     </row>
-    <row r="154" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="77" t="s">
         <v>52</v>
       </c>
@@ -11316,7 +11319,7 @@
       <c r="AA154" s="33"/>
       <c r="AB154" s="18"/>
     </row>
-    <row r="155" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="12" t="s">
         <v>25</v>
       </c>
@@ -11367,7 +11370,7 @@
       <c r="AA155" s="33"/>
       <c r="AB155" s="18"/>
     </row>
-    <row r="156" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="12" t="s">
         <v>25</v>
       </c>
@@ -11410,7 +11413,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="82" t="s">
         <v>34</v>
       </c>
@@ -11457,7 +11460,7 @@
       <c r="U157" s="78"/>
       <c r="V157" s="84"/>
     </row>
-    <row r="158" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="82" t="s">
         <v>34</v>
       </c>
@@ -11504,7 +11507,7 @@
       <c r="U158" s="84"/>
       <c r="V158" s="78"/>
     </row>
-    <row r="159" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="4" t="s">
         <v>42</v>
       </c>
@@ -11551,7 +11554,7 @@
       <c r="U159" s="4"/>
       <c r="V159" s="31"/>
     </row>
-    <row r="160" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="4" t="s">
         <v>42</v>
       </c>
@@ -11598,7 +11601,7 @@
       <c r="U160" s="31"/>
       <c r="V160" s="4"/>
     </row>
-    <row r="161" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="82" t="s">
         <v>44</v>
       </c>
@@ -11645,7 +11648,7 @@
       <c r="U161" s="78"/>
       <c r="V161" s="84"/>
     </row>
-    <row r="162" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="82" t="s">
         <v>44</v>
       </c>
@@ -11692,7 +11695,7 @@
       <c r="U162" s="84"/>
       <c r="V162" s="78"/>
     </row>
-    <row r="163" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="74" t="s">
         <v>46</v>
       </c>
@@ -11739,7 +11742,7 @@
       <c r="U163" s="4"/>
       <c r="V163" s="31"/>
     </row>
-    <row r="164" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="74" t="s">
         <v>46</v>
       </c>
@@ -11786,7 +11789,7 @@
       <c r="U164" s="31"/>
       <c r="V164" s="4"/>
     </row>
-    <row r="165" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="82" t="s">
         <v>48</v>
       </c>
@@ -11833,7 +11836,7 @@
       <c r="U165" s="78"/>
       <c r="V165" s="84"/>
     </row>
-    <row r="166" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="82" t="s">
         <v>48</v>
       </c>
@@ -11880,7 +11883,7 @@
       <c r="U166" s="84"/>
       <c r="V166" s="78"/>
     </row>
-    <row r="167" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="12" t="s">
         <v>50</v>
       </c>
@@ -11927,7 +11930,7 @@
       <c r="U167" s="4"/>
       <c r="V167" s="31"/>
     </row>
-    <row r="168" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="77" t="s">
         <v>52</v>
       </c>
@@ -11974,7 +11977,7 @@
       <c r="U168" s="78"/>
       <c r="V168" s="84"/>
     </row>
-    <row r="169" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="77" t="s">
         <v>52</v>
       </c>
@@ -12021,7 +12024,7 @@
       <c r="U169" s="84"/>
       <c r="V169" s="78"/>
     </row>
-    <row r="170" spans="1:151" s="49" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:151" s="49" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="18"/>
       <c r="B170" s="12" t="s">
         <v>25</v>
@@ -12194,7 +12197,7 @@
       <c r="ET170" s="18"/>
       <c r="EU170" s="18"/>
     </row>
-    <row r="171" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="18"/>
       <c r="B171" s="82" t="s">
         <v>34</v>
@@ -12369,7 +12372,7 @@
       <c r="ET171" s="18"/>
       <c r="EU171" s="18"/>
     </row>
-    <row r="172" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="18"/>
       <c r="B172" s="4" t="s">
         <v>42</v>
@@ -12544,7 +12547,7 @@
       <c r="ET172" s="18"/>
       <c r="EU172" s="18"/>
     </row>
-    <row r="173" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="18"/>
       <c r="B173" s="82" t="s">
         <v>44</v>
@@ -12719,7 +12722,7 @@
       <c r="ET173" s="18"/>
       <c r="EU173" s="18"/>
     </row>
-    <row r="174" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="18"/>
       <c r="B174" s="74" t="s">
         <v>46</v>
@@ -12894,7 +12897,7 @@
       <c r="ET174" s="18"/>
       <c r="EU174" s="18"/>
     </row>
-    <row r="175" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="18"/>
       <c r="B175" s="82" t="s">
         <v>48</v>
@@ -13069,7 +13072,7 @@
       <c r="ET175" s="18"/>
       <c r="EU175" s="18"/>
     </row>
-    <row r="176" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="18"/>
       <c r="B176" s="12" t="s">
         <v>50</v>
@@ -13244,7 +13247,7 @@
       <c r="ET176" s="18"/>
       <c r="EU176" s="18"/>
     </row>
-    <row r="177" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="18"/>
       <c r="B177" s="77" t="s">
         <v>52</v>
@@ -13290,7 +13293,7 @@
       <c r="U177" s="78"/>
       <c r="V177" s="84"/>
     </row>
-    <row r="178" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="36"/>
       <c r="B178" s="89" t="s">
         <v>25</v>
@@ -13335,7 +13338,7 @@
       <c r="V178" s="90"/>
       <c r="W178" s="26"/>
     </row>
-    <row r="179" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="89" t="s">
         <v>25</v>
       </c>
@@ -13378,7 +13381,7 @@
       <c r="U179" s="95"/>
       <c r="V179" s="95"/>
     </row>
-    <row r="180" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="96" t="s">
         <v>34</v>
       </c>
@@ -13423,7 +13426,7 @@
       <c r="U180" s="101"/>
       <c r="V180" s="101"/>
     </row>
-    <row r="181" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="96" t="s">
         <v>34</v>
       </c>
@@ -13470,7 +13473,7 @@
       <c r="U181" s="101"/>
       <c r="V181" s="101"/>
     </row>
-    <row r="182" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="96" t="s">
         <v>34</v>
       </c>
@@ -13515,7 +13518,7 @@
       <c r="U182" s="101"/>
       <c r="V182" s="101"/>
     </row>
-    <row r="183" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="90" t="s">
         <v>42</v>
       </c>
@@ -13560,7 +13563,7 @@
       <c r="U183" s="95"/>
       <c r="V183" s="95"/>
     </row>
-    <row r="184" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="90" t="s">
         <v>42</v>
       </c>
@@ -13607,7 +13610,7 @@
       <c r="U184" s="95"/>
       <c r="V184" s="95"/>
     </row>
-    <row r="185" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="90" t="s">
         <v>42</v>
       </c>
@@ -13652,7 +13655,7 @@
       <c r="U185" s="95"/>
       <c r="V185" s="95"/>
     </row>
-    <row r="186" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B186" s="96" t="s">
         <v>44</v>
       </c>
@@ -13697,7 +13700,7 @@
       <c r="U186" s="101"/>
       <c r="V186" s="101"/>
     </row>
-    <row r="187" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="96" t="s">
         <v>44</v>
       </c>
@@ -13744,7 +13747,7 @@
       <c r="U187" s="101"/>
       <c r="V187" s="101"/>
     </row>
-    <row r="188" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="96" t="s">
         <v>44</v>
       </c>
@@ -13789,7 +13792,7 @@
       <c r="U188" s="101"/>
       <c r="V188" s="101"/>
     </row>
-    <row r="189" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="93" t="s">
         <v>46</v>
       </c>
@@ -13834,7 +13837,7 @@
       <c r="U189" s="95"/>
       <c r="V189" s="95"/>
     </row>
-    <row r="190" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B190" s="93" t="s">
         <v>46</v>
       </c>
@@ -13881,7 +13884,7 @@
       <c r="U190" s="95"/>
       <c r="V190" s="95"/>
     </row>
-    <row r="191" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="93" t="s">
         <v>46</v>
       </c>
@@ -13926,7 +13929,7 @@
       <c r="U191" s="95"/>
       <c r="V191" s="95"/>
     </row>
-    <row r="192" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="102" t="s">
         <v>50</v>
       </c>
@@ -13971,7 +13974,7 @@
       <c r="U192" s="101"/>
       <c r="V192" s="101"/>
     </row>
-    <row r="193" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="102" t="s">
         <v>50</v>
       </c>
@@ -14018,7 +14021,7 @@
       <c r="U193" s="101"/>
       <c r="V193" s="101"/>
     </row>
-    <row r="194" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="92" t="s">
         <v>52</v>
       </c>
@@ -14063,7 +14066,7 @@
       <c r="U194" s="92"/>
       <c r="V194" s="92"/>
     </row>
-    <row r="195" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="92" t="s">
         <v>52</v>
       </c>
@@ -14110,7 +14113,7 @@
       <c r="U195" s="92"/>
       <c r="V195" s="92"/>
     </row>
-    <row r="196" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="62" t="s">
         <v>25</v>
       </c>
@@ -14157,7 +14160,7 @@
       <c r="U196" s="60"/>
       <c r="V196" s="60"/>
     </row>
-    <row r="197" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="76" t="s">
         <v>34</v>
       </c>
@@ -14204,7 +14207,7 @@
       <c r="U197" s="65"/>
       <c r="V197" s="65"/>
     </row>
-    <row r="198" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="76" t="s">
         <v>34</v>
       </c>
@@ -14251,7 +14254,7 @@
       <c r="U198" s="65"/>
       <c r="V198" s="65"/>
     </row>
-    <row r="199" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B199" s="62" t="s">
         <v>42</v>
       </c>
@@ -14298,7 +14301,7 @@
       <c r="U199" s="62"/>
       <c r="V199" s="62"/>
     </row>
-    <row r="200" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B200" s="62" t="s">
         <v>42</v>
       </c>
@@ -14345,7 +14348,7 @@
       <c r="U200" s="62"/>
       <c r="V200" s="62"/>
     </row>
-    <row r="201" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B201" s="75" t="s">
         <v>44</v>
       </c>
@@ -14392,7 +14395,7 @@
       <c r="U201" s="39"/>
       <c r="V201" s="39"/>
     </row>
-    <row r="202" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B202" s="75" t="s">
         <v>44</v>
       </c>
@@ -14439,7 +14442,7 @@
       <c r="U202" s="39"/>
       <c r="V202" s="39"/>
     </row>
-    <row r="203" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B203" s="62" t="s">
         <v>46</v>
       </c>
@@ -14486,7 +14489,7 @@
       <c r="U203" s="62"/>
       <c r="V203" s="62"/>
     </row>
-    <row r="204" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B204" s="62" t="s">
         <v>46</v>
       </c>
@@ -14533,7 +14536,7 @@
       <c r="U204" s="62"/>
       <c r="V204" s="62"/>
     </row>
-    <row r="205" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B205" s="75" t="s">
         <v>50</v>
       </c>
@@ -14580,7 +14583,7 @@
       <c r="U205" s="37"/>
       <c r="V205" s="37"/>
     </row>
-    <row r="206" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B206" s="62" t="s">
         <v>52</v>
       </c>
@@ -14627,7 +14630,7 @@
       <c r="U206" s="62"/>
       <c r="V206" s="62"/>
     </row>
-    <row r="207" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B207" s="62" t="s">
         <v>52</v>
       </c>
@@ -14674,7 +14677,7 @@
       <c r="U207" s="62"/>
       <c r="V207" s="62"/>
     </row>
-    <row r="208" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B208" s="12" t="s">
         <v>25</v>
       </c>
@@ -14723,7 +14726,7 @@
       <c r="AA208" s="33"/>
       <c r="AB208" s="18"/>
     </row>
-    <row r="209" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B209" s="82" t="s">
         <v>34</v>
       </c>
@@ -14770,7 +14773,7 @@
       <c r="U209" s="78"/>
       <c r="V209" s="84"/>
     </row>
-    <row r="210" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B210" s="82" t="s">
         <v>34</v>
       </c>
@@ -14817,7 +14820,7 @@
       <c r="U210" s="84"/>
       <c r="V210" s="78"/>
     </row>
-    <row r="211" spans="1:151" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:151" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>42</v>
       </c>
@@ -14864,7 +14867,7 @@
       <c r="U211" s="4"/>
       <c r="V211" s="31"/>
     </row>
-    <row r="212" spans="1:151" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:151" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>42</v>
       </c>
@@ -14911,7 +14914,7 @@
       <c r="U212" s="31"/>
       <c r="V212" s="4"/>
     </row>
-    <row r="213" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="82" t="s">
         <v>44</v>
       </c>
@@ -14958,7 +14961,7 @@
       <c r="U213" s="78"/>
       <c r="V213" s="84"/>
     </row>
-    <row r="214" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B214" s="82" t="s">
         <v>44</v>
       </c>
@@ -15005,7 +15008,7 @@
       <c r="U214" s="84"/>
       <c r="V214" s="78"/>
     </row>
-    <row r="215" spans="1:151" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:151" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B215" s="74" t="s">
         <v>46</v>
       </c>
@@ -15052,7 +15055,7 @@
       <c r="U215" s="4"/>
       <c r="V215" s="31"/>
     </row>
-    <row r="216" spans="1:151" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:151" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B216" s="74" t="s">
         <v>46</v>
       </c>
@@ -15099,7 +15102,7 @@
       <c r="U216" s="31"/>
       <c r="V216" s="4"/>
     </row>
-    <row r="217" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B217" s="82" t="s">
         <v>48</v>
       </c>
@@ -15146,7 +15149,7 @@
       <c r="U217" s="78"/>
       <c r="V217" s="84"/>
     </row>
-    <row r="218" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B218" s="82" t="s">
         <v>48</v>
       </c>
@@ -15193,7 +15196,7 @@
       <c r="U218" s="84"/>
       <c r="V218" s="78"/>
     </row>
-    <row r="219" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B219" s="12" t="s">
         <v>50</v>
       </c>
@@ -15240,7 +15243,7 @@
       <c r="U219" s="4"/>
       <c r="V219" s="31"/>
     </row>
-    <row r="220" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B220" s="77" t="s">
         <v>52</v>
       </c>
@@ -15289,7 +15292,7 @@
       <c r="U220" s="78"/>
       <c r="V220" s="84"/>
     </row>
-    <row r="221" spans="1:151" s="49" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:151" s="49" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="18"/>
       <c r="B221" s="12" t="s">
         <v>25</v>
@@ -15462,7 +15465,7 @@
       <c r="ET221" s="18"/>
       <c r="EU221" s="18"/>
     </row>
-    <row r="222" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="18"/>
       <c r="B222" s="82" t="s">
         <v>34</v>
@@ -15641,7 +15644,7 @@
       <c r="ET222" s="18"/>
       <c r="EU222" s="18"/>
     </row>
-    <row r="223" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="18"/>
       <c r="B223" s="4" t="s">
         <v>42</v>
@@ -15820,7 +15823,7 @@
       <c r="ET223" s="18"/>
       <c r="EU223" s="18"/>
     </row>
-    <row r="224" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="18"/>
       <c r="B224" s="82" t="s">
         <v>44</v>
@@ -15999,7 +16002,7 @@
       <c r="ET224" s="18"/>
       <c r="EU224" s="18"/>
     </row>
-    <row r="225" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="18"/>
       <c r="B225" s="74" t="s">
         <v>46</v>
@@ -16178,7 +16181,7 @@
       <c r="ET225" s="18"/>
       <c r="EU225" s="18"/>
     </row>
-    <row r="226" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="18"/>
       <c r="B226" s="82" t="s">
         <v>48</v>
@@ -16357,7 +16360,7 @@
       <c r="ET226" s="18"/>
       <c r="EU226" s="18"/>
     </row>
-    <row r="227" spans="1:151" s="50" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:151" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="18"/>
       <c r="B227" s="12" t="s">
         <v>50</v>
@@ -16536,7 +16539,7 @@
       <c r="ET227" s="18"/>
       <c r="EU227" s="18"/>
     </row>
-    <row r="228" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="18"/>
       <c r="B228" s="77" t="s">
         <v>52</v>
@@ -16586,7 +16589,7 @@
       <c r="U228" s="78"/>
       <c r="V228" s="84"/>
     </row>
-    <row r="229" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B229" s="12" t="s">
         <v>25</v>
       </c>
@@ -16631,7 +16634,7 @@
       <c r="U229" s="31"/>
       <c r="V229" s="4"/>
     </row>
-    <row r="230" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B230" s="82" t="s">
         <v>34</v>
       </c>
@@ -16688,7 +16691,7 @@
       <c r="U230" s="78"/>
       <c r="V230" s="84"/>
     </row>
-    <row r="231" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B231" s="4" t="s">
         <v>42</v>
       </c>
@@ -16745,7 +16748,7 @@
       <c r="U231" s="4"/>
       <c r="V231" s="31"/>
     </row>
-    <row r="232" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B232" s="82" t="s">
         <v>44</v>
       </c>
@@ -16802,7 +16805,7 @@
       <c r="U232" s="78"/>
       <c r="V232" s="84"/>
     </row>
-    <row r="233" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B233" s="74" t="s">
         <v>46</v>
       </c>
@@ -16859,7 +16862,7 @@
       <c r="U233" s="4"/>
       <c r="V233" s="31"/>
     </row>
-    <row r="234" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B234" s="82" t="s">
         <v>48</v>
       </c>
@@ -16916,7 +16919,7 @@
       <c r="U234" s="78"/>
       <c r="V234" s="84"/>
     </row>
-    <row r="235" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B235" s="12" t="s">
         <v>50</v>
       </c>
@@ -16973,7 +16976,7 @@
       <c r="U235" s="4"/>
       <c r="V235" s="31"/>
     </row>
-    <row r="236" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B236" s="77" t="s">
         <v>52</v>
       </c>
@@ -17030,7 +17033,7 @@
       <c r="U236" s="78"/>
       <c r="V236" s="84"/>
     </row>
-    <row r="237" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B237" s="12" t="s">
         <v>25</v>
       </c>
@@ -17073,7 +17076,7 @@
       <c r="U237" s="31"/>
       <c r="V237" s="4"/>
     </row>
-    <row r="238" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B238" s="82" t="s">
         <v>34</v>
       </c>
@@ -17116,7 +17119,7 @@
       <c r="U238" s="78"/>
       <c r="V238" s="84"/>
     </row>
-    <row r="239" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B239" s="4" t="s">
         <v>42</v>
       </c>
@@ -17159,7 +17162,7 @@
       <c r="U239" s="4"/>
       <c r="V239" s="31"/>
     </row>
-    <row r="240" spans="1:151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:151" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B240" s="82" t="s">
         <v>44</v>
       </c>
@@ -17202,7 +17205,7 @@
       <c r="U240" s="78"/>
       <c r="V240" s="84"/>
     </row>
-    <row r="241" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B241" s="74" t="s">
         <v>46</v>
       </c>
@@ -17245,7 +17248,7 @@
       <c r="U241" s="4"/>
       <c r="V241" s="31"/>
     </row>
-    <row r="242" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B242" s="82" t="s">
         <v>48</v>
       </c>
@@ -17288,7 +17291,7 @@
       <c r="U242" s="78"/>
       <c r="V242" s="84"/>
     </row>
-    <row r="243" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B243" s="12" t="s">
         <v>50</v>
       </c>
@@ -17331,7 +17334,7 @@
       <c r="U243" s="4"/>
       <c r="V243" s="31"/>
     </row>
-    <row r="244" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="77" t="s">
         <v>52</v>
       </c>
@@ -17374,7 +17377,7 @@
       <c r="U244" s="78"/>
       <c r="V244" s="84"/>
     </row>
-    <row r="245" spans="2:28" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:28" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="12" t="s">
         <v>25</v>
       </c>
@@ -17426,7 +17429,7 @@
       <c r="X245" s="26"/>
       <c r="Y245" s="26"/>
     </row>
-    <row r="246" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B246" s="12" t="s">
         <v>25</v>
       </c>
@@ -17481,7 +17484,7 @@
       <c r="AA246" s="26"/>
       <c r="AB246" s="34"/>
     </row>
-    <row r="247" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B247" s="82" t="s">
         <v>34</v>
       </c>
@@ -17542,7 +17545,7 @@
       <c r="AA247" s="26"/>
       <c r="AB247" s="34"/>
     </row>
-    <row r="248" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="82" t="s">
         <v>34</v>
       </c>
@@ -17599,7 +17602,7 @@
       <c r="AA248" s="18"/>
       <c r="AB248" s="18"/>
     </row>
-    <row r="249" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="82" t="s">
         <v>34</v>
       </c>
@@ -17660,7 +17663,7 @@
       <c r="AA249" s="18"/>
       <c r="AB249" s="18"/>
     </row>
-    <row r="250" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B250" s="82" t="s">
         <v>34</v>
       </c>
@@ -17717,7 +17720,7 @@
       <c r="AA250" s="18"/>
       <c r="AB250" s="18"/>
     </row>
-    <row r="251" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B251" s="74" t="s">
         <v>42</v>
       </c>
@@ -17778,7 +17781,7 @@
       <c r="AA251" s="26"/>
       <c r="AB251" s="34"/>
     </row>
-    <row r="252" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B252" s="74" t="s">
         <v>42</v>
       </c>
@@ -17835,7 +17838,7 @@
       <c r="AA252" s="18"/>
       <c r="AB252" s="18"/>
     </row>
-    <row r="253" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B253" s="74" t="s">
         <v>42</v>
       </c>
@@ -17896,7 +17899,7 @@
       <c r="AA253" s="18"/>
       <c r="AB253" s="18"/>
     </row>
-    <row r="254" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B254" s="74" t="s">
         <v>42</v>
       </c>
@@ -17953,7 +17956,7 @@
       <c r="AA254" s="18"/>
       <c r="AB254" s="18"/>
     </row>
-    <row r="255" spans="2:28" s="1" customFormat="1" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:28" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B255" s="82" t="s">
         <v>44</v>
       </c>
@@ -18014,7 +18017,7 @@
       <c r="AA255" s="26"/>
       <c r="AB255" s="34"/>
     </row>
-    <row r="256" spans="2:28" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B256" s="82" t="s">
         <v>44</v>
       </c>
@@ -18071,7 +18074,7 @@
       <c r="AA256" s="18"/>
       <c r="AB256" s="18"/>
     </row>
-    <row r="257" spans="2:28" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B257" s="82" t="s">
         <v>44</v>
       </c>
@@ -18132,7 +18135,7 @@
       <c r="AA257" s="18"/>
       <c r="AB257" s="18"/>
     </row>
-    <row r="258" spans="2:28" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B258" s="82" t="s">
         <v>44</v>
       </c>
@@ -18189,7 +18192,7 @@
       <c r="AA258" s="18"/>
       <c r="AB258" s="18"/>
     </row>
-    <row r="259" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B259" s="74" t="s">
         <v>46</v>
       </c>
@@ -18250,7 +18253,7 @@
       <c r="AA259" s="26"/>
       <c r="AB259" s="34"/>
     </row>
-    <row r="260" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B260" s="74" t="s">
         <v>46</v>
       </c>
@@ -18307,7 +18310,7 @@
       <c r="AA260" s="18"/>
       <c r="AB260" s="18"/>
     </row>
-    <row r="261" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B261" s="74" t="s">
         <v>46</v>
       </c>
@@ -18368,7 +18371,7 @@
       <c r="AA261" s="18"/>
       <c r="AB261" s="18"/>
     </row>
-    <row r="262" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B262" s="74" t="s">
         <v>46</v>
       </c>
@@ -18425,7 +18428,7 @@
       <c r="AA262" s="18"/>
       <c r="AB262" s="18"/>
     </row>
-    <row r="263" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B263" s="82" t="s">
         <v>48</v>
       </c>
@@ -18486,7 +18489,7 @@
       <c r="AA263" s="26"/>
       <c r="AB263" s="34"/>
     </row>
-    <row r="264" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B264" s="82" t="s">
         <v>48</v>
       </c>
@@ -18543,7 +18546,7 @@
       <c r="AA264" s="18"/>
       <c r="AB264" s="18"/>
     </row>
-    <row r="265" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B265" s="82" t="s">
         <v>48</v>
       </c>
@@ -18604,7 +18607,7 @@
       <c r="AA265" s="18"/>
       <c r="AB265" s="18"/>
     </row>
-    <row r="266" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B266" s="82" t="s">
         <v>48</v>
       </c>
@@ -18661,7 +18664,7 @@
       <c r="AA266" s="18"/>
       <c r="AB266" s="18"/>
     </row>
-    <row r="267" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B267" s="74" t="s">
         <v>50</v>
       </c>
@@ -18722,7 +18725,7 @@
       <c r="AA267" s="26"/>
       <c r="AB267" s="34"/>
     </row>
-    <row r="268" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B268" s="74" t="s">
         <v>50</v>
       </c>
@@ -18779,7 +18782,7 @@
       <c r="AA268" s="18"/>
       <c r="AB268" s="18"/>
     </row>
-    <row r="269" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B269" s="74" t="s">
         <v>50</v>
       </c>
@@ -18840,7 +18843,7 @@
       <c r="AA269" s="18"/>
       <c r="AB269" s="18"/>
     </row>
-    <row r="270" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B270" s="74" t="s">
         <v>50</v>
       </c>
@@ -18897,7 +18900,7 @@
       <c r="AA270" s="18"/>
       <c r="AB270" s="18"/>
     </row>
-    <row r="271" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B271" s="77" t="s">
         <v>52</v>
       </c>
@@ -18958,7 +18961,7 @@
       <c r="AA271" s="18"/>
       <c r="AB271" s="18"/>
     </row>
-    <row r="272" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B272" s="77" t="s">
         <v>52</v>
       </c>
@@ -19013,7 +19016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="2:28" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:28" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B273" s="12" t="s">
         <v>25</v>
       </c>
@@ -19063,7 +19066,7 @@
       <c r="X273" s="26"/>
       <c r="Y273" s="26"/>
     </row>
-    <row r="274" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B274" s="82" t="s">
         <v>34</v>
       </c>
@@ -19120,7 +19123,7 @@
       <c r="AA274" s="26"/>
       <c r="AB274" s="34"/>
     </row>
-    <row r="275" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B275" s="82" t="s">
         <v>34</v>
       </c>
@@ -19175,7 +19178,7 @@
       <c r="AA275" s="18"/>
       <c r="AB275" s="18"/>
     </row>
-    <row r="276" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B276" s="82" t="s">
         <v>34</v>
       </c>
@@ -19230,7 +19233,7 @@
       <c r="AA276" s="18"/>
       <c r="AB276" s="18"/>
     </row>
-    <row r="277" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B277" s="82" t="s">
         <v>34</v>
       </c>
@@ -19285,7 +19288,7 @@
       <c r="AA277" s="18"/>
       <c r="AB277" s="18"/>
     </row>
-    <row r="278" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B278" s="74" t="s">
         <v>42</v>
       </c>
@@ -19342,7 +19345,7 @@
       <c r="AA278" s="26"/>
       <c r="AB278" s="34"/>
     </row>
-    <row r="279" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B279" s="74" t="s">
         <v>42</v>
       </c>
@@ -19397,7 +19400,7 @@
       <c r="AA279" s="18"/>
       <c r="AB279" s="18"/>
     </row>
-    <row r="280" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B280" s="74" t="s">
         <v>42</v>
       </c>
@@ -19452,7 +19455,7 @@
       <c r="AA280" s="18"/>
       <c r="AB280" s="18"/>
     </row>
-    <row r="281" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B281" s="74" t="s">
         <v>42</v>
       </c>
@@ -19507,7 +19510,7 @@
       <c r="AA281" s="18"/>
       <c r="AB281" s="18"/>
     </row>
-    <row r="282" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B282" s="82" t="s">
         <v>44</v>
       </c>
@@ -19564,7 +19567,7 @@
       <c r="AA282" s="26"/>
       <c r="AB282" s="34"/>
     </row>
-    <row r="283" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B283" s="82" t="s">
         <v>44</v>
       </c>
@@ -19619,7 +19622,7 @@
       <c r="AA283" s="18"/>
       <c r="AB283" s="18"/>
     </row>
-    <row r="284" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B284" s="82" t="s">
         <v>44</v>
       </c>
@@ -19674,7 +19677,7 @@
       <c r="AA284" s="18"/>
       <c r="AB284" s="18"/>
     </row>
-    <row r="285" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B285" s="82" t="s">
         <v>44</v>
       </c>
@@ -19729,7 +19732,7 @@
       <c r="AA285" s="18"/>
       <c r="AB285" s="18"/>
     </row>
-    <row r="286" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B286" s="74" t="s">
         <v>46</v>
       </c>
@@ -19786,7 +19789,7 @@
       <c r="AA286" s="26"/>
       <c r="AB286" s="34"/>
     </row>
-    <row r="287" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B287" s="74" t="s">
         <v>46</v>
       </c>
@@ -19841,7 +19844,7 @@
       <c r="AA287" s="18"/>
       <c r="AB287" s="18"/>
     </row>
-    <row r="288" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B288" s="74" t="s">
         <v>46</v>
       </c>
@@ -19896,7 +19899,7 @@
       <c r="AA288" s="18"/>
       <c r="AB288" s="18"/>
     </row>
-    <row r="289" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B289" s="74" t="s">
         <v>46</v>
       </c>
@@ -19951,7 +19954,7 @@
       <c r="AA289" s="18"/>
       <c r="AB289" s="18"/>
     </row>
-    <row r="290" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B290" s="82" t="s">
         <v>48</v>
       </c>
@@ -20008,7 +20011,7 @@
       <c r="AA290" s="26"/>
       <c r="AB290" s="34"/>
     </row>
-    <row r="291" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B291" s="82" t="s">
         <v>48</v>
       </c>
@@ -20063,7 +20066,7 @@
       <c r="AA291" s="18"/>
       <c r="AB291" s="18"/>
     </row>
-    <row r="292" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B292" s="82" t="s">
         <v>48</v>
       </c>
@@ -20118,7 +20121,7 @@
       <c r="AA292" s="18"/>
       <c r="AB292" s="18"/>
     </row>
-    <row r="293" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B293" s="82" t="s">
         <v>48</v>
       </c>
@@ -20173,7 +20176,7 @@
       <c r="AA293" s="18"/>
       <c r="AB293" s="18"/>
     </row>
-    <row r="294" spans="2:28" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B294" s="74" t="s">
         <v>50</v>
       </c>
@@ -20230,7 +20233,7 @@
       <c r="AA294" s="26"/>
       <c r="AB294" s="34"/>
     </row>
-    <row r="295" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="74" t="s">
         <v>50</v>
       </c>
@@ -20285,7 +20288,7 @@
       <c r="AA295" s="18"/>
       <c r="AB295" s="18"/>
     </row>
-    <row r="296" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="74" t="s">
         <v>50</v>
       </c>
@@ -20340,7 +20343,7 @@
       <c r="AA296" s="18"/>
       <c r="AB296" s="18"/>
     </row>
-    <row r="297" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="74" t="s">
         <v>50</v>
       </c>
@@ -20395,7 +20398,7 @@
       <c r="AA297" s="18"/>
       <c r="AB297" s="18"/>
     </row>
-    <row r="298" spans="2:28" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="77" t="s">
         <v>52</v>
       </c>
@@ -20454,24 +20457,7 @@
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="aYF+aV6dtII6Y0PHslHv6oUVErB7FT0nN6hq0NKxVrGbDZpUA/y1kg4BQTz02rSv21TKOdhEXpF31qsqHWq58A==" saltValue="1NOBKeZkJ9QBoCe8UgGxgg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="B5:K298" xr:uid="{DF8C699D-BC39-450F-9879-6A3CE12FA813}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="001-002"/>
-        <filter val="003-004"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="19mm"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="SI (SP)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B5:K298" xr:uid="{DF8C699D-BC39-450F-9879-6A3CE12FA813}"/>
   <mergeCells count="5">
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:N2"/>
@@ -20523,12 +20509,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="116"/>
-      <c r="C1" s="117" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
       <c r="G1" s="57"/>
       <c r="H1" s="57"/>
       <c r="I1" s="57"/>
@@ -20552,10 +20538,10 @@
       <c r="AD1" s="36"/>
     </row>
     <row r="2" spans="2:30" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
       <c r="AD2" s="36"/>
     </row>
     <row r="3" spans="2:30" ht="14.4" x14ac:dyDescent="0.3">
@@ -20569,19 +20555,19 @@
       <c r="G4" s="1"/>
       <c r="H4"/>
       <c r="I4"/>
-      <c r="N4" s="118" t="s">
+      <c r="N4" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
       <c r="Y4" s="35"/>
       <c r="AD4" s="36"/>
     </row>
@@ -35966,12 +35952,12 @@
       <c r="H4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="118" t="s">
+      <c r="I4" s="122" t="s">
         <v>342</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
     </row>
     <row r="5" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
@@ -36498,12 +36484,12 @@
       <c r="H22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="118" t="s">
+      <c r="I22" s="122" t="s">
         <v>342</v>
       </c>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+      <c r="J22" s="122"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
     </row>
     <row r="23" spans="2:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
@@ -37690,12 +37676,12 @@
       <c r="H63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I63" s="118" t="s">
+      <c r="I63" s="122" t="s">
         <v>342</v>
       </c>
-      <c r="J63" s="118"/>
-      <c r="K63" s="118"/>
-      <c r="L63" s="118"/>
+      <c r="J63" s="122"/>
+      <c r="K63" s="122"/>
+      <c r="L63" s="122"/>
     </row>
     <row r="64" spans="2:12" s="17" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="12" t="s">
